--- a/data/trans_dic/IP16A10-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,85</t>
+          <t>0,0; 12,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,97</t>
+          <t>0,0; 9,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,2</t>
+          <t>0,0; 10,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,27</t>
+          <t>0,0; 5,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>0,0; 6,81</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 15,54</t>
+          <t>2,75; 15,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,73</t>
+          <t>1,12; 11,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,01</t>
+          <t>0,0; 9,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,73</t>
+          <t>1,27; 8,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,91</t>
+          <t>1,17; 7,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,19</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,28; 28,82</t>
+          <t>6,46; 28,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,19</t>
+          <t>0,0; 10,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,58</t>
+          <t>0,0; 8,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,96</t>
+          <t>0,0; 12,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,94</t>
+          <t>0,0; 9,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 17,1</t>
+          <t>2,05; 16,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 16,17</t>
+          <t>4,26; 15,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,96</t>
+          <t>0,66; 6,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,93</t>
+          <t>1,04; 9,3</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,78</t>
+          <t>0,0; 11,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,03</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,49</t>
+          <t>2,76; 9,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,07</t>
+          <t>0,6; 4,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,97</t>
+          <t>0,34; 2,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,52</t>
+          <t>0,46; 4,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,6</t>
+          <t>0,98; 4,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,3</t>
+          <t>0,44; 3,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,59</t>
+          <t>2,03; 5,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,44</t>
+          <t>0,97; 3,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,56</t>
+          <t>0,43; 2,56</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2722</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3986</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2698</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4547</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4140</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3476</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1147; 6519</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>581; 5968</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4599</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1051; 6638</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1197; 7641</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3896</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2620</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2675</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1627; 7112</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4434</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3052</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4218</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4736</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>664; 5454</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2568; 9379</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>623; 6365</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>687; 6168</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4295</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3260</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>6797</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3296</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>7394</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3459; 11637</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1123; 7525</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>558; 4656</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>669; 6158</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1875; 8700</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>659; 5451</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5470; 14693</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3667; 13254</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1349; 7953</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A10-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Habitat-trans_dic.xlsx
@@ -688,17 +688,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,18</t>
+          <t>0,0; 12,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,49</t>
+          <t>0,0; 9,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 10,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,81</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 15,65</t>
+          <t>2,62; 14,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 11,54</t>
+          <t>1,13; 10,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,02</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 8,0</t>
+          <t>1,33; 7,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,44</t>
+          <t>1,22; 7,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 28,26</t>
+          <t>6,77; 28,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,21</t>
+          <t>0,0; 9,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,99</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,01</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,36</t>
+          <t>0,0; 10,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 16,85</t>
+          <t>2,03; 15,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 15,56</t>
+          <t>4,14; 16,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,77</t>
+          <t>0,66; 6,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,3</t>
+          <t>1,04; 9,01</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,06</t>
+          <t>0,0; 9,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,29</t>
+          <t>2,85; 8,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,02</t>
+          <t>0,64; 3,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,86</t>
+          <t>0,34; 2,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,28</t>
+          <t>0,47; 4,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,56</t>
+          <t>0,69; 4,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,68</t>
+          <t>0,44; 3,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,46</t>
+          <t>2,13; 5,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,51</t>
+          <t>1,01; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,56</t>
+          <t>0,45; 2,53</t>
         </is>
       </c>
     </row>
@@ -1427,17 +1427,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 3895</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2722</t>
+          <t>0; 2826</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3986</t>
+          <t>0; 3937</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2698</t>
+          <t>0; 3372</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 4567</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4140</t>
+          <t>0; 3759</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1147; 6519</t>
+          <t>1091; 6088</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>581; 5968</t>
+          <t>584; 5492</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4599</t>
+          <t>0; 4530</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1051; 6638</t>
+          <t>1104; 6557</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1197; 7641</t>
+          <t>1251; 8086</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1627; 7112</t>
+          <t>1703; 7263</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4434</t>
+          <t>0; 4241</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3052</t>
+          <t>0; 2842</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4218</t>
+          <t>0; 4494</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4736</t>
+          <t>0; 5060</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>664; 5454</t>
+          <t>656; 5151</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2568; 9379</t>
+          <t>2493; 9674</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>623; 6365</t>
+          <t>620; 6400</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>687; 6168</t>
+          <t>687; 5979</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4295</t>
+          <t>0; 3600</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3260</t>
+          <t>0; 3424</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3459; 11637</t>
+          <t>3573; 11072</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1123; 7525</t>
+          <t>1193; 7245</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558; 4656</t>
+          <t>557; 4794</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>669; 6158</t>
+          <t>683; 6916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1875; 8700</t>
+          <t>1314; 8057</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>659; 5451</t>
+          <t>656; 5618</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5470; 14693</t>
+          <t>5721; 14906</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3667; 13254</t>
+          <t>3803; 13004</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1349; 7953</t>
+          <t>1393; 7846</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A10-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Habitat-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+          <t>Menores que consumieron  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,58%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,68</t>
+          <t>0,0; 5,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,96%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,2%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,61</t>
+          <t>0,0; 9,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,69; 15,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,89</t>
+          <t>1,13; 10,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,9</t>
+          <t>1,35; 7,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,87</t>
+          <t>1,24; 7,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>15,48%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 28,86</t>
+          <t>0,0; 13,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,77</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,37</t>
+          <t>2,03; 17,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>8,28; 28,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,0</t>
+          <t>0,0; 9,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 15,91</t>
+          <t>0,0; 12,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 16,05</t>
+          <t>4,18; 16,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,81</t>
+          <t>0,65; 6,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,01</t>
+          <t>1,05; 9,93</t>
         </is>
       </c>
     </row>
@@ -955,22 +955,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 6,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,84</t>
+          <t>0,46; 4,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,87</t>
+          <t>0,81; 4,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,95</t>
+          <t>0,45; 3,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,81</t>
+          <t>3,04; 9,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,22</t>
+          <t>0,65; 4,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,79</t>
+          <t>0,34; 2,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,54</t>
+          <t>2,13; 5,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,44</t>
+          <t>1,04; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,53</t>
+          <t>0,45; 2,56</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+          <t>Menores que consumieron  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>1149</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4005</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4013</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3895</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2826</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3937</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3480</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3372</t>
+          <t>0; 4424</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4567</t>
+          <t>0; 4234</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3759</t>
+          <t>0; 4000</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,27 +1527,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2900</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2171</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1305</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1091; 6088</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>584; 5492</t>
+          <t>0; 4592</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1122; 6472</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>585; 5554</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1104; 6557</t>
+          <t>1120; 6416</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1251; 8086</t>
+          <t>1275; 8125</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>3896</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1126</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>613</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1494</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1703; 7263</t>
+          <t>0; 4905</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4241</t>
+          <t>0; 5029</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2842</t>
+          <t>657; 5536</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4494</t>
+          <t>2084; 7253</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5060</t>
+          <t>0; 3990</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>656; 5151</t>
+          <t>0; 4271</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2493; 9674</t>
+          <t>2517; 9746</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>620; 6400</t>
+          <t>613; 6546</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>687; 5979</t>
+          <t>697; 6583</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>685</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3410</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3600</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3424</t>
+          <t>0; 3887</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1963,27 +1963,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>6797</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1762</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3573; 11072</t>
+          <t>669; 6504</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1193; 7245</t>
+          <t>1547; 8784</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>557; 4794</t>
+          <t>661; 4881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>683; 6916</t>
+          <t>3809; 11888</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1314; 8057</t>
+          <t>1211; 7613</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>656; 5618</t>
+          <t>554; 4830</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5721; 14906</t>
+          <t>5723; 15037</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3803; 13004</t>
+          <t>3915; 12980</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1393; 7846</t>
+          <t>1392; 7948</t>
         </is>
       </c>
     </row>
